--- a/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260706_211916.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260706_211916.xlsx
@@ -6408,7 +6408,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6630,7 +6630,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6996,7 +6996,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260706_211916.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260706_211916.xlsx
@@ -6408,7 +6408,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6630,7 +6630,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6996,7 +6996,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
